--- a/data/delivery/集群设备配置表.xlsx
+++ b/data/delivery/集群设备配置表.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
